--- a/data/output/2025-05/智慧停车运营报告_202505.xlsx
+++ b/data/output/2025-05/智慧停车运营报告_202505.xlsx
@@ -16,6 +16,7 @@
     <sheet name="异常清单" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="待办事项" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="负责人待办" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="发送记录" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -545,7 +546,301 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>10</v>
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>发送时间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>问题数量</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>发送状态</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>失败原因</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>耗时(秒)</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>统计月份</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260607_064142</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:41:42</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1302,7 +1597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1323,30 +1618,45 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>总车次</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>平均停车时长(小时)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>总停车时长(小时)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>统计天数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>车位利用率(%)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>数据状态</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>早高峰占用率(%)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>晚高峰占用率(%)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>平均高峰占用率(%)</t>
         </is>
@@ -1367,22 +1677,39 @@
         <v>150</v>
       </c>
       <c r="D2" t="n">
-        <v>2.29</v>
+        <v>8805</v>
       </c>
       <c r="E2" t="n">
-        <v>64.06</v>
+        <v>2.25</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06</v>
+        <v>19818.19</v>
       </c>
       <c r="G2" t="n">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="H2" t="n">
-        <v>78</v>
-      </c>
-      <c r="I2" t="n">
-        <v>73</v>
+        <v>19.66</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1400,22 +1727,39 @@
         <v>200</v>
       </c>
       <c r="D3" t="n">
-        <v>2.84</v>
+        <v>6758</v>
       </c>
       <c r="E3" t="n">
-        <v>87.90000000000001</v>
+        <v>2.85</v>
       </c>
       <c r="F3" t="n">
-        <v>0.06</v>
+        <v>19283.92</v>
       </c>
       <c r="G3" t="n">
-        <v>84</v>
+        <v>31</v>
       </c>
       <c r="H3" t="n">
-        <v>74</v>
-      </c>
-      <c r="I3" t="n">
-        <v>79</v>
+        <v>12.96</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1433,22 +1777,39 @@
         <v>250</v>
       </c>
       <c r="D4" t="n">
-        <v>2.58</v>
+        <v>5211</v>
       </c>
       <c r="E4" t="n">
-        <v>79.92</v>
+        <v>2.55</v>
       </c>
       <c r="F4" t="n">
-        <v>0.04</v>
+        <v>13308.68</v>
       </c>
       <c r="G4" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="H4" t="n">
-        <v>82</v>
-      </c>
-      <c r="I4" t="n">
-        <v>74.5</v>
+        <v>7.16</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1466,22 +1827,39 @@
         <v>300</v>
       </c>
       <c r="D5" t="n">
+        <v>5724</v>
+      </c>
+      <c r="E5" t="n">
         <v>2.46</v>
       </c>
-      <c r="E5" t="n">
-        <v>76.33</v>
-      </c>
       <c r="F5" t="n">
-        <v>0.03</v>
+        <v>14094.3</v>
       </c>
       <c r="G5" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>89</v>
-      </c>
-      <c r="I5" t="n">
-        <v>89</v>
+        <v>6.31</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1499,88 +1877,139 @@
         <v>400</v>
       </c>
       <c r="D6" t="n">
-        <v>2.51</v>
+        <v>5208</v>
       </c>
       <c r="E6" t="n">
-        <v>77.84999999999999</v>
+        <v>2.47</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03</v>
+        <v>12884.2</v>
       </c>
       <c r="G6" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="H6" t="n">
-        <v>72</v>
-      </c>
-      <c r="I6" t="n">
-        <v>79.5</v>
+        <v>4.33</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>万达广场委托车场</t>
+          <t>火车站直营停车场</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>委托</t>
+          <t>直营</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="D7" t="n">
-        <v>2.41</v>
+        <v>6310</v>
       </c>
       <c r="E7" t="n">
-        <v>74.62</v>
+        <v>2.46</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>15505.86</v>
       </c>
       <c r="G7" t="n">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="H7" t="n">
-        <v>94</v>
-      </c>
-      <c r="I7" t="n">
-        <v>84</v>
+        <v>3.47</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>火车站直营停车场</t>
+          <t>万达广场委托车场</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>直营</t>
+          <t>委托</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>600</v>
+        <v>500</v>
       </c>
       <c r="D8" t="n">
-        <v>2.45</v>
+        <v>4977</v>
       </c>
       <c r="E8" t="n">
-        <v>75.91</v>
+        <v>2.43</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02</v>
+        <v>12070.27</v>
       </c>
       <c r="G8" t="n">
-        <v>77</v>
+        <v>31</v>
       </c>
       <c r="H8" t="n">
-        <v>72</v>
-      </c>
-      <c r="I8" t="n">
-        <v>74.5</v>
+        <v>3.24</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>数据不足</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +2289,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1899,6 +2328,16 @@
           <t>异常日期</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>问题类型</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1932,6 +2371,8 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1969,6 +2410,8 @@
           <t>2025-05-29</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2006,6 +2449,8 @@
           <t>2025-05-13</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2043,6 +2488,8 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2080,6 +2527,8 @@
           <t>2025-05-24</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2117,6 +2566,8 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2154,6 +2605,8 @@
           <t>2025-05-15</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2191,6 +2644,8 @@
           <t>2025-05-12</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2228,6 +2683,8 @@
           <t>2025-05-05</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2263,6 +2720,197 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>2025-05-19</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2925,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2318,15 +2966,25 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>问题类型</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>问题描述</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>处理状态</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>截止日期</t>
         </is>
@@ -2364,17 +3022,19 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2416,17 +3076,19 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2468,17 +3130,19 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2520,17 +3184,19 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2572,17 +3238,19 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2624,17 +3292,19 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2676,17 +3346,19 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2728,17 +3400,19 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2780,17 +3454,19 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2832,17 +3508,313 @@
           <t>2025-05-19</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -2859,7 +3831,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2883,6 +3855,11 @@
           <t>严重程度</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>问题数量</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2905,6 +3882,9 @@
           <t>中, 高</t>
         </is>
       </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2927,6 +3907,9 @@
           <t>中</t>
         </is>
       </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2949,6 +3932,9 @@
           <t>中</t>
         </is>
       </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2971,6 +3957,9 @@
           <t>中</t>
         </is>
       </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2993,6 +3982,9 @@
           <t>中</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3015,6 +4007,9 @@
           <t>中</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3036,6 +4031,9 @@
         <is>
           <t>中</t>
         </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/2025-05/智慧停车运营报告_202505.xlsx
+++ b/data/output/2025-05/智慧停车运营报告_202505.xlsx
@@ -16,7 +16,8 @@
     <sheet name="异常清单" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="待办事项" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="负责人待办" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="发送记录" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="通知复盘" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="发送记录" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -560,7 +561,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -571,49 +572,59 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>统计月份</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>应发问题数</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>实际发送数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>是否未发送问题</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>发送状态</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>发送范围</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>失败原因</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>发送时间</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>负责人</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>问题数量</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>发送状态</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>失败原因</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>耗时(秒)</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>统计月份</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -622,32 +633,42 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -656,32 +677,42 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -690,32 +721,42 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E4" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -724,32 +765,42 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -758,32 +809,42 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="n">
-        <v>0</v>
-      </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -792,32 +853,42 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="n">
-        <v>0</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260607_064142</t>
+          <t>20260607_065312</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-06-07 06:41:42</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -826,18 +897,362 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>成功</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="n">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>发送时间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>发送模式</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>问题数量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>发送状态</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>失败原因</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>耗时(秒)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>统计月份</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>20260607_065312</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2026-06-07 06:53:12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>simulate</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>成功</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
@@ -2289,7 +2704,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2330,12 +2745,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>问题类型</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>问题描述</t>
+          <t>统计月份</t>
         </is>
       </c>
     </row>
@@ -2371,8 +2781,11 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2410,8 +2823,11 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2449,8 +2865,11 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2488,8 +2907,11 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2527,8 +2949,11 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2566,8 +2991,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2605,8 +3033,11 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2644,8 +3075,11 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2683,8 +3117,11 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2722,8 +3159,11 @@
           <t>2025-05-19</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2731,24 +3171,31 @@
           <t>万达广场委托车场</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2758,24 +3205,31 @@
           <t>中心广场直营停车场</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2785,24 +3239,31 @@
           <t>商业中心委托车场</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2812,24 +3273,31 @@
           <t>商业街直营-收入异常_202505</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2839,24 +3307,31 @@
           <t>居民区委托-缺失日期_202505</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2866,24 +3341,31 @@
           <t>火车站直营停车场</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2893,24 +3375,31 @@
           <t>科技园A区直营_202505</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>缺少字段</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>2025-05</t>
         </is>
       </c>
     </row>
@@ -2925,7 +3414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2966,25 +3455,20 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>问题类型</t>
+          <t>统计月份</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>问题描述</t>
+          <t>处理状态</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>处理状态</t>
+          <t>优先级</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>优先级</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>截止日期</t>
         </is>
@@ -3022,19 +3506,22 @@
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3076,19 +3563,22 @@
           <t>2025-05-29</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3130,19 +3620,22 @@
           <t>2025-05-13</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3184,19 +3677,22 @@
           <t>2025-05-07</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3238,19 +3734,22 @@
           <t>2025-05-24</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3292,19 +3791,22 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3346,19 +3848,22 @@
           <t>2025-05-15</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P0</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
-        <is>
-          <t>P0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3400,19 +3905,22 @@
           <t>2025-05-12</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3454,19 +3962,22 @@
           <t>2025-05-05</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3508,19 +4019,22 @@
           <t>2025-05-19</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3532,37 +4046,44 @@
           <t>万达广场委托车场</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3574,37 +4095,44 @@
           <t>中心广场直营停车场</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3616,37 +4144,44 @@
           <t>商业中心委托车场</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3658,37 +4193,44 @@
           <t>商业街直营-收入异常_202505</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3700,37 +4242,44 @@
           <t>居民区委托-缺失日期_202505</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3742,37 +4291,44 @@
           <t>火车站直营停车场</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3784,37 +4340,44 @@
           <t>科技园A区直营_202505</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
           <t>中</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>缺少字段</t>
+          <t>2025-05</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>待处理</t>
+          <t>P1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3869,7 +4432,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>收入突降</t>
+          <t>收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -3883,7 +4446,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -3894,7 +4457,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>缺失日期, 收入突降</t>
+          <t>缺失日期, 收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -3908,7 +4471,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -3919,7 +4482,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>收入突降</t>
+          <t>收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -3933,7 +4496,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -3944,7 +4507,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>收入突降</t>
+          <t>收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -3958,7 +4521,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -3969,7 +4532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>收入突降</t>
+          <t>收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -3983,7 +4546,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -3994,7 +4557,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>收入突降</t>
+          <t>收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4008,7 +4571,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -4019,7 +4582,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>收入突降</t>
+          <t>收入突降, 缺少字段</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4033,7 +4596,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data/output/2025-05/智慧停车运营报告_202505.xlsx
+++ b/data/output/2025-05/智慧停车运营报告_202505.xlsx
@@ -17,7 +17,9 @@
     <sheet name="待办事项" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="负责人待办" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="通知复盘" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="发送记录" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="闭环复盘" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="反馈异常" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="消息预览" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -619,7 +621,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -645,7 +647,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>已预览</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -656,14 +658,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -680,34 +682,38 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>未发送</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>目标范围</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>范围外</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>本次运行未执行发送</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -733,7 +739,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>已预览</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -744,14 +750,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -768,34 +774,38 @@
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>未发送</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>目标范围</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>范围外</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>本次运行未执行发送</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -812,34 +822,38 @@
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>未发送</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>目标范围</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>范围外</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>本次运行未执行发送</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -856,34 +870,38 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>未发送</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>目标范围</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>范围外</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>本次运行未执行发送</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -900,27 +918,31 @@
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>成功</t>
+          <t>未发送</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>目标范围</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>范围外</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>本次运行未执行发送</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
     </row>
@@ -935,70 +957,455 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>批次ID</t>
+          <t>负责人</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>发送时间</t>
+          <t>本月新增问题数</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>发送模式</t>
+          <t>历史未关闭数</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>负责人</t>
+          <t>本月已关闭数</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>问题数量</t>
+          <t>超期未处理数</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>发送状态</t>
+          <t>复发问题数</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>失败原因</t>
+          <t>问题总数</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>耗时(秒)</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>统计月份</t>
+          <t>本月闭环率(%)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="n">
+        <v>2</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>孙八</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>33.33</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>张三</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>李四</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>王五</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>赵六</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>钱七</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>合计</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>15</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E9" t="n">
+        <v>15</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>17</v>
+      </c>
+      <c r="H9" t="n">
+        <v>11.76</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>问题ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>处理状态</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>错误原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NONEXIST001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>驳回</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>simulate</t>
+          <t>运营人员2</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-06-05 10:00:00</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>这是第5条处理反馈，状态为驳回</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>问题ID不存在或不匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NONEXIST002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>驳回</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>运营人员3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>2025-06-06 10:00:00</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>这是第6条处理反馈，状态为驳回</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>问题ID不存在或不匹配</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>批次ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>生成时间</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>发送模式</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>问题数量</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>消息主题</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>消息内容</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>统计月份</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>20260607_071007</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:10:07</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>preview</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1011,14 +1418,63 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="inlineStr">
+          <t>【智慧停车运营月报】2025年05月 (未关闭2项, 复发1项) - 周九</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尊敬的 周九 您好：
+您负责的车场在 2025年05月 运营检查中发现以下待处理问题：
+━━━━━━━━━━━━━━━━━━━━━━━
+📊 问题概览
+━━━━━━━━━━━━━━━━━━━━━━━
+  总计异常: 3 项
+  🔴 高优先级: 1 项
+  🟡 中优先级: 2 项
+  🟢 低优先级: 0 项
+  🆕 新增问题: 0 项
+  ⏳ 历史未关闭: 2 项
+  🔁 复发问题: 1 项
+🏢 涉及车场: 商业街直营-收入异常_202505
+📋 问题类型: 收入突降, 缺少字段
+━━━━━━━━━━━━━━━━━━━━━━━
+📝 异常明细
+━━━━━━━━━━━━━━━━━━━━━━━
+🟡 [1] 收入突降 🔁 (重复3次) [首次发现:2025-05]
+    车场: 商业街直营-收入异常_202505
+    描述: 当日收入较7日均值下降 32.9%
+    详情: 当日收入: ¥4309.78, 7日均值: ¥6420.45
+    日期: 2025-05-12
+    问题ID: 64825C28
+    ─────────────────────────────
+🔴 [2] 收入突降 ⏳ (重复3次) [首次发现:2025-05]
+    车场: 商业街直营-收入异常_202505
+    描述: 当日收入较7日均值下降 73.7%
+    详情: 当日收入: ¥1441.01, 7日均值: ¥5480.54
+    日期: 2025-05-15
+    问题ID: 568751B9
+    ─────────────────────────────
+🟡 [3] 缺少字段 ⏳ (重复3次) [首次发现:2025-05]
+    车场: 商业街直营-收入异常_202505
+    描述: 缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率
+    日期: 
+    问题ID: 328570EF
+    ─────────────────────────────
+━━━━━━━━━━━━━━━━━━━━━━━
+📌 处理要求
+━━━━━━━━━━━━━━━━━━━━━━━
+  • 高优先级问题请在 3 个工作日内处理
+  • 中优先级问题请在 7 个工作日内处理
+  • 处理完成后请在系统中更新状态
+  • 🔁标记为复发的问题请重点关注根因分析
+如有疑问请联系运营管理部门。
+--
+智慧停车月度运营自动化工具
+生成时间: 2026-06-07 07:10:07
+</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
@@ -1027,232 +1483,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260607_065312</t>
+          <t>20260607_071007</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07 06:53:12</t>
+          <t>2026-06-07 07:10:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>simulate</t>
+          <t>preview</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>孙八</t>
+          <t>张三</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20260607_065312</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-06-07 06:53:12</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>simulate</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>张三</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>20260607_065312</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-06-07 06:53:12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>simulate</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>李四</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>20260607_065312</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-06-07 06:53:12</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>simulate</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>王五</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>20260607_065312</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-06-07 06:53:12</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>simulate</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>赵六</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>20260607_065312</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-06-07 06:53:12</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>simulate</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>钱七</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>成功</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
+          <t>【智慧停车运营月报】2025年05月 (未关闭2项) - 张三</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">尊敬的 张三 您好：
+您负责的车场在 2025年05月 运营检查中发现以下待处理问题：
+━━━━━━━━━━━━━━━━━━━━━━━
+📊 问题概览
+━━━━━━━━━━━━━━━━━━━━━━━
+  总计异常: 2 项
+  🔴 高优先级: 0 项
+  🟡 中优先级: 2 项
+  🟢 低优先级: 0 项
+  🆕 新增问题: 0 项
+  ⏳ 历史未关闭: 2 项
+  🔁 复发问题: 0 项
+🏢 涉及车场: 中心广场直营停车场
+📋 问题类型: 收入突降, 缺少字段
+━━━━━━━━━━━━━━━━━━━━━━━
+📝 异常明细
+━━━━━━━━━━━━━━━━━━━━━━━
+🟡 [1] 收入突降 ⏳ (重复3次) [首次发现:2025-05]
+    车场: 中心广场直营停车场
+    描述: 当日收入较7日均值下降 33.0%
+    详情: 当日收入: ¥3719.81, 7日均值: ¥5548.43
+    日期: 2025-05-13
+    问题ID: 32E4E9A3
+    ─────────────────────────────
+🟡 [2] 缺少字段 ⏳ (重复3次) [首次发现:2025-05]
+    车场: 中心广场直营停车场
+    描述: 缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率
+    日期: 
+    问题ID: 8A8BD349
+    ─────────────────────────────
+━━━━━━━━━━━━━━━━━━━━━━━
+📌 处理要求
+━━━━━━━━━━━━━━━━━━━━━━━
+  • 高优先级问题请在 3 个工作日内处理
+  • 中优先级问题请在 7 个工作日内处理
+  • 处理完成后请在系统中更新状态
+  • 🔁标记为复发的问题请重点关注根因分析
+如有疑问请联系运营管理部门。
+--
+智慧停车月度运营自动化工具
+生成时间: 2026-06-07 07:10:07
+</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
         <is>
           <t>2025-05</t>
         </is>
@@ -2704,7 +3007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2745,7 +3048,42 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>统计月份</t>
+          <t>问题ID</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>问题来源</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>重复出现次数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>首次发现月份</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>处理状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
         </is>
       </c>
     </row>
@@ -2783,7 +3121,40 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>复发问题</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>运营人员1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-06-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>这是第1条处理反馈，状态为已处理</t>
         </is>
       </c>
     </row>
@@ -2825,9 +3196,30 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>027774C8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2867,7 +3259,40 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>运营人员3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-06-03 10:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>这是第3条处理反馈，状态为处理中</t>
         </is>
       </c>
     </row>
@@ -2909,9 +3334,30 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2951,9 +3397,30 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2993,7 +3460,40 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>复发问题</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>运营人员2</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-06-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>这是第2条处理反馈，状态为已处理</t>
         </is>
       </c>
     </row>
@@ -3035,9 +3535,30 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3077,9 +3598,30 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3119,9 +3661,30 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3161,9 +3724,30 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3195,7 +3779,40 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>运营人员1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-06-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>这是第4条处理反馈，状态为处理中</t>
         </is>
       </c>
     </row>
@@ -3229,9 +3846,30 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3263,9 +3901,30 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3297,9 +3956,30 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3331,9 +4011,30 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3365,9 +4066,30 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3399,9 +4121,30 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3414,7 +4157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:Q18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3455,20 +4198,50 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>统计月份</t>
+          <t>问题ID</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>问题来源</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>重复出现次数</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>首次发现月份</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>处理状态</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>截止日期</t>
         </is>
@@ -3508,20 +4281,48 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>复发问题</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>运营人员1</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-06-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>这是第1条处理反馈，状态为已处理</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3565,20 +4366,36 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>027774C8</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>3</v>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3622,20 +4439,48 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>3</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>运营人员3</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-06-03 10:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>这是第3条处理反馈，状态为处理中</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3679,20 +4524,36 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3736,20 +4597,36 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3793,20 +4670,48 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>复发问题</t>
+        </is>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>运营人员2</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-06-02 10:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>这是第2条处理反馈，状态为已处理</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3850,20 +4755,36 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>3</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3907,20 +4828,36 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>3</v>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -3964,20 +4901,36 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4021,20 +4974,36 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4070,20 +5039,48 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>运营人员1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-06-04 10:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>这是第4条处理反馈，状态为处理中</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4119,20 +5116,36 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4168,20 +5181,36 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4217,20 +5246,36 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>3</v>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4266,20 +5311,36 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4315,20 +5376,36 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4364,20 +5441,36 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>历史未关闭</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>2025-05</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4394,7 +5487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4420,6 +5513,11 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>处理状态汇总</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>问题数量</t>
         </is>
       </c>
@@ -4445,7 +5543,12 @@
           <t>中, 高</t>
         </is>
       </c>
-      <c r="E2" t="n">
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>已处理, 待处理</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4470,7 +5573,12 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E3" t="n">
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>已处理, 待处理</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4495,7 +5603,12 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>处理中, 待处理</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4520,7 +5633,12 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E5" t="n">
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>待处理, 处理中</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4545,7 +5663,12 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="F6" t="n">
         <v>2</v>
       </c>
     </row>
@@ -4570,7 +5693,12 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4595,7 +5723,12 @@
           <t>中</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>2</v>
       </c>
     </row>

--- a/data/output/2025-05/智慧停车运营报告_202505.xlsx
+++ b/data/output/2025-05/智慧停车运营报告_202505.xlsx
@@ -18,8 +18,10 @@
     <sheet name="负责人待办" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="通知复盘" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="闭环复盘" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="反馈异常" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="消息预览" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="问题生命周期" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="反馈待确认" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="反馈异常" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="消息预览" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -621,7 +623,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -658,14 +660,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -682,38 +684,34 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>未发送</t>
+          <t>已预览</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>范围外</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>本次运行未执行发送</t>
-        </is>
-      </c>
+          <t>目标范围</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -730,34 +728,38 @@
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>已预览</t>
+          <t>未发送</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>目标范围</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>范围外</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>本次运行未执行发送</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -798,14 +800,14 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -846,14 +848,14 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -894,14 +896,14 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -942,7 +944,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
     </row>
@@ -957,7 +959,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -983,20 +985,35 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>复发问题数</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>超期未处理数</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>复发问题数</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>即将超期数</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>平均处理天数</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>最长未处理天数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>问题总数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>本月闭环率(%)</t>
         </is>
@@ -1012,22 +1029,31 @@
         <v>0</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>402</v>
+      </c>
+      <c r="J2" t="n">
         <v>3</v>
       </c>
-      <c r="H2" t="n">
-        <v>33.33</v>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1046,15 +1072,24 @@
         <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>402</v>
+      </c>
+      <c r="J3" t="n">
         <v>3</v>
       </c>
-      <c r="H3" t="n">
+      <c r="K3" t="n">
         <v>33.33</v>
       </c>
     </row>
@@ -1074,17 +1109,26 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
+      <c r="I4" t="n">
+        <v>402</v>
+      </c>
+      <c r="J4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1102,17 +1146,26 @@
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
+      <c r="I5" t="n">
+        <v>402</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1130,17 +1183,26 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
+      <c r="I6" t="n">
+        <v>402</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1158,17 +1220,26 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
       </c>
+      <c r="I7" t="n">
+        <v>402</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1186,17 +1257,26 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
       </c>
+      <c r="I8" t="n">
+        <v>402</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1208,22 +1288,31 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
+        <v>402</v>
+      </c>
+      <c r="J9" t="n">
         <v>17</v>
       </c>
-      <c r="H9" t="n">
-        <v>11.76</v>
+      <c r="K9" t="n">
+        <v>5.88</v>
       </c>
     </row>
   </sheetData>
@@ -1237,7 +1326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1248,91 +1337,2501 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>处理状态</t>
+          <t>事件类型</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>处理人</t>
+          <t>事件时间</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>处理时间</t>
+          <t>事件描述</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>备注</t>
+          <t>操作人</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>错误原因</t>
+          <t>关联批次</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>车场名称</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NONEXIST001</t>
+          <t>027774C8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>驳回</t>
+          <t>首次发现</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>运营人员2</t>
+          <t>2026-06-07 07:22:23</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-05 10:00:00</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>这是第5条处理反馈，状态为驳回</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>问题ID不存在或不匹配</t>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 31.5%</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>收入突降</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NONEXIST002</t>
+          <t>027774C8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>驳回</t>
+          <t>重复出现</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>运营人员3</t>
+          <t>2026-06-07 07:22:53</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-06-06 10:00:00</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>这是第6条处理反馈，状态为驳回</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>问题ID不存在或不匹配</t>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>027774C8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>027774C8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>328570EF</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 33.0%</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>32E4E9A3</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 33.2%</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>420F6E59</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 73.7%</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>568751B9</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 33.0%</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>63128535</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 32.9%</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>64825C28</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>商业街直营-收入异常_202505</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>76FADA64</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 32.2%</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>83F42648</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>状态变更: 待处理 → 驳回，备注: 数据不全无法处理</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>运营3</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>状态变更: 驳回 → 驳回，备注: 数据不全无法处理</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>运营3</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>8A8BD349</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>中心广场直营停车场</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 34.8%</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>8B8B3509</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>2025-06-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>状态变更: 待处理 → 已处理，备注: 已补全缺失日期数据</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>处理反馈</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>2025-06-01 10:00:00</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>状态变更: 已处理 → 已处理，备注: 已补全缺失日期数据</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>首次发现: 缺失日期 - 缺失 3 天数据</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺失日期</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺失日期</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>A1FF648C</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺失日期</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>缺失日期</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>ACEBC597</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>科技园A区直营_202505</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>B650CAD8</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>火车站直营停车场</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C52D79B1</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>万达广场委托车场</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>首次发现: 收入突降 - 当日收入较7日均值下降 32.3%</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>第2次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>第3次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>EE567A10</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>第4次出现: 收入突降</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>商业中心委托车场</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>首次发现</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:23</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>首次发现: 缺少字段 - 缺少入场时间(entry_time), 出场时间(exit_</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:22:53</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>第2次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:39</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>第3次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>F4951FEF</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>重复出现</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>2026-06-07 07:23:49</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>第4次出现: 缺少字段</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>居民区委托-缺失日期_202505</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
         </is>
       </c>
     </row>
@@ -1347,6 +3846,287 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:J3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>车场名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>异常描述</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>处理状态</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>候选问题数</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>候选问题ID</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>商业街直营</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>运营2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-06-02 14:30:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>收入突降已查明原因</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>64825C28;568751B9</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>收入突降</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>运营4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-06-05 11:00:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>多条收入突降已处理</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>9</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>027774C8;32E4E9A3;EE567A10;83F42648;64825C28;568751B9;63128535;8B8B3509;420F6E59</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>车场名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>负责人</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>异常类型</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>异常描述</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>处理状态</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>处理人</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>处理时间</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>错误原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>周九</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>缺少字段</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>处理中</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2025-06-03 09:00:00</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>正在补充字段</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>问题ID不存在或无法匹配</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>不存在的车场</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>已处理</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>运营5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2025-06-06 15:00:00</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>测试无法匹配的反馈</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>问题ID不存在或无法匹配</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -1395,12 +4175,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1418,7 +4198,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>【智慧停车运营月报】2025年05月 (未关闭2项, 复发1项) - 周九</t>
+          <t>【智慧停车运营月报】2025年05月 (未关闭3项) - 周九</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1433,28 +4213,30 @@
   🟡 中优先级: 2 项
   🟢 低优先级: 0 项
   🆕 新增问题: 0 项
-  ⏳ 历史未关闭: 2 项
-  🔁 复发问题: 1 项
+  ⏳ 历史未关闭: 3 项
+  🔁 复发问题: 0 项
+  ⚠️ 即将超期: 0 项
+  ❌ 已超期: 0 项
 🏢 涉及车场: 商业街直营-收入异常_202505
 📋 问题类型: 收入突降, 缺少字段
 ━━━━━━━━━━━━━━━━━━━━━━━
-📝 异常明细
+⏳ 历史未关闭问题
 ━━━━━━━━━━━━━━━━━━━━━━━
-🟡 [1] 收入突降 🔁 (重复3次) [首次发现:2025-05]
+🟡 [1] 收入突降 ⏳ (重复4次) [首次发现:2025-05] [截止:2026-06-14]
     车场: 商业街直营-收入异常_202505
     描述: 当日收入较7日均值下降 32.9%
     详情: 当日收入: ¥4309.78, 7日均值: ¥6420.45
     日期: 2025-05-12
     问题ID: 64825C28
     ─────────────────────────────
-🔴 [2] 收入突降 ⏳ (重复3次) [首次发现:2025-05]
+🔴 [2] 收入突降 ⏳ (重复4次) [首次发现:2025-05] [截止:2026-06-10]
     车场: 商业街直营-收入异常_202505
     描述: 当日收入较7日均值下降 73.7%
     详情: 当日收入: ¥1441.01, 7日均值: ¥5480.54
     日期: 2025-05-15
     问题ID: 568751B9
     ─────────────────────────────
-🟡 [3] 缺少字段 ⏳ (重复3次) [首次发现:2025-05]
+🟡 [3] 缺少字段 ⏳ (重复4次) [首次发现:2025-05] [截止:2026-06-14]
     车场: 商业街直营-收入异常_202505
     描述: 缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率
     日期: 
@@ -1463,14 +4245,16 @@
 ━━━━━━━━━━━━━━━━━━━━━━━
 📌 处理要求
 ━━━━━━━━━━━━━━━━━━━━━━━
-  • 高优先级问题请在 3 个工作日内处理
-  • 中优先级问题请在 7 个工作日内处理
-  • 处理完成后请在系统中更新状态
-  • 🔁标记为复发的问题请重点关注根因分析
+  • 🔴 高优先级问题请在 3 个工作日内处理
+  • 🟡 中优先级问题请在 7 个工作日内处理
+  • 🟢 低优先级问题请在 15 个工作日内处理
+  • ❌ 已超期问题请立即处理并说明原因
+  • 🔁 复发问题请重点关注根因分析，避免再次出现
+处理完成后请在系统中更新处理状态和备注。
 如有疑问请联系运营管理部门。
 --
 智慧停车月度运营自动化工具
-生成时间: 2026-06-07 07:10:07
+生成时间: 2026-06-07 07:23:49
 </t>
         </is>
       </c>
@@ -1483,12 +4267,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260607_071007</t>
+          <t>20260607_072349</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-06-07 07:10:07</t>
+          <t>2026-06-07 07:23:49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1498,60 +4282,73 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>张三</t>
+          <t>孙八</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>【智慧停车运营月报】2025年05月 (未关闭2项) - 张三</t>
+          <t>【智慧停车运营月报】2025年05月 (未关闭2项, 复发1项) - 孙八</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t xml:space="preserve">尊敬的 张三 您好：
+          <t xml:space="preserve">尊敬的 孙八 您好：
 您负责的车场在 2025年05月 运营检查中发现以下待处理问题：
 ━━━━━━━━━━━━━━━━━━━━━━━
 📊 问题概览
 ━━━━━━━━━━━━━━━━━━━━━━━
-  总计异常: 2 项
+  总计异常: 3 项
   🔴 高优先级: 0 项
-  🟡 中优先级: 2 项
+  🟡 中优先级: 3 项
   🟢 低优先级: 0 项
   🆕 新增问题: 0 项
   ⏳ 历史未关闭: 2 项
-  🔁 复发问题: 0 项
-🏢 涉及车场: 中心广场直营停车场
-📋 问题类型: 收入突降, 缺少字段
+  🔁 复发问题: 1 项
+  ⚠️ 即将超期: 0 项
+  ❌ 已超期: 0 项
+🏢 涉及车场: 居民区委托-缺失日期_202505
+📋 问题类型: 缺失日期, 收入突降, 缺少字段
 ━━━━━━━━━━━━━━━━━━━━━━━
-📝 异常明细
+⏳ 历史未关闭问题
 ━━━━━━━━━━━━━━━━━━━━━━━
-🟡 [1] 收入突降 ⏳ (重复3次) [首次发现:2025-05]
-    车场: 中心广场直营停车场
+🟡 [1] 收入突降 ⏳ (重复4次) [首次发现:2025-05] [截止:2026-06-14]
+    车场: 居民区委托-缺失日期_202505
     描述: 当日收入较7日均值下降 33.0%
-    详情: 当日收入: ¥3719.81, 7日均值: ¥5548.43
-    日期: 2025-05-13
-    问题ID: 32E4E9A3
+    详情: 当日收入: ¥2992.04, 7日均值: ¥4462.94
+    日期: 2025-05-12
+    问题ID: 63128535
     ─────────────────────────────
-🟡 [2] 缺少字段 ⏳ (重复3次) [首次发现:2025-05]
-    车场: 中心广场直营停车场
+🟡 [2] 缺少字段 ⏳ (重复4次) [首次发现:2025-05] [截止:2026-06-14]
+    车场: 居民区委托-缺失日期_202505
     描述: 缺少入场时间(entry_time), 出场时间(exit_time)，无法计算高峰占用率
     日期: 
-    问题ID: 8A8BD349
+    问题ID: F4951FEF
+    ─────────────────────────────
+━━━━━━━━━━━━━━━━━━━━━━━
+🔁 复发问题
+━━━━━━━━━━━━━━━━━━━━━━━
+🟡 [1] 缺失日期 🔁 (重复4次) [首次发现:2025-05] [截止:2026-06-14]
+    车场: 居民区委托-缺失日期_202505
+    描述: 缺失 3 天数据
+    详情: 2025-05-02, 2025-05-08, 2025-05-17
+    问题ID: A1FF648C
     ─────────────────────────────
 ━━━━━━━━━━━━━━━━━━━━━━━
 📌 处理要求
 ━━━━━━━━━━━━━━━━━━━━━━━
-  • 高优先级问题请在 3 个工作日内处理
-  • 中优先级问题请在 7 个工作日内处理
-  • 处理完成后请在系统中更新状态
-  • 🔁标记为复发的问题请重点关注根因分析
+  • 🔴 高优先级问题请在 3 个工作日内处理
+  • 🟡 中优先级问题请在 7 个工作日内处理
+  • 🟢 低优先级问题请在 15 个工作日内处理
+  • ❌ 已超期问题请立即处理并说明原因
+  • 🔁 复发问题请重点关注根因分析，避免再次出现
+处理完成后请在系统中更新处理状态和备注。
 如有疑问请联系运营管理部门。
 --
 智慧停车月度运营自动化工具
-生成时间: 2026-06-07 07:10:07
+生成时间: 2026-06-07 07:23:49
 </t>
         </is>
       </c>
@@ -2170,7 +4967,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2186,19 +4983,19 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>临停收入</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>月卡收入</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>总收入</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>临停收入</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>月卡收入</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>总车次</t>
@@ -2206,27 +5003,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>会员总数</t>
+          <t>免费车次</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>总车位数</t>
+          <t>平均车场收入</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>平均单场收入</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>会员覆盖率(%)</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>月卡收入占比(%)</t>
+          <t>免费率</t>
         </is>
       </c>
     </row>
@@ -2240,31 +5027,25 @@
         <v>3</v>
       </c>
       <c r="C2" t="n">
+        <v>553157.88</v>
+      </c>
+      <c r="D2" t="n">
+        <v>40389.99</v>
+      </c>
+      <c r="E2" t="n">
         <v>593547.87</v>
-      </c>
-      <c r="D2" t="n">
-        <v>553157.88</v>
-      </c>
-      <c r="E2" t="n">
-        <v>40389.99</v>
       </c>
       <c r="F2" t="n">
         <v>18990</v>
       </c>
       <c r="G2" t="n">
-        <v>544</v>
+        <v>1186</v>
       </c>
       <c r="H2" t="n">
-        <v>1050</v>
+        <v>197849.29</v>
       </c>
       <c r="I2" t="n">
-        <v>197849.29</v>
-      </c>
-      <c r="J2" t="n">
-        <v>51.81</v>
-      </c>
-      <c r="K2" t="n">
-        <v>6.8</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="3">
@@ -2277,31 +5058,25 @@
         <v>4</v>
       </c>
       <c r="C3" t="n">
+        <v>673746.17</v>
+      </c>
+      <c r="D3" t="n">
+        <v>54259.04</v>
+      </c>
+      <c r="E3" t="n">
         <v>728005.21</v>
-      </c>
-      <c r="D3" t="n">
-        <v>673746.17</v>
-      </c>
-      <c r="E3" t="n">
-        <v>54259.04</v>
       </c>
       <c r="F3" t="n">
         <v>24003</v>
       </c>
       <c r="G3" t="n">
-        <v>686</v>
+        <v>1529</v>
       </c>
       <c r="H3" t="n">
-        <v>1350</v>
+        <v>182001.3</v>
       </c>
       <c r="I3" t="n">
-        <v>182001.3</v>
-      </c>
-      <c r="J3" t="n">
-        <v>50.81</v>
-      </c>
-      <c r="K3" t="n">
-        <v>7.45</v>
+        <v>6.37</v>
       </c>
     </row>
   </sheetData>
@@ -3007,7 +5782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:R18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3068,20 +5843,35 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>超期状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>剩余天数</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>建议处理期限</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>处理状态</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>处理人</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>处理时间</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
@@ -3130,7 +5920,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -3139,22 +5929,35 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>已处理</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>运营人员1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2025-06-01 10:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>这是第1条处理反馈，状态为已处理</t>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>已补全缺失日期数据</t>
         </is>
       </c>
     </row>
@@ -3205,7 +6008,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -3214,12 +6017,25 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -3268,7 +6084,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -3277,24 +6093,25 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>运营人员3</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-06-03 10:00:00</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>这是第3条处理反馈，状态为处理中</t>
-        </is>
-      </c>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -3343,7 +6160,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -3352,12 +6169,25 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -3406,7 +6236,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -3415,12 +6245,25 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -3465,11 +6308,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>复发问题</t>
+          <t>历史未关闭</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -3478,24 +6321,25 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>运营人员2</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-06-02 10:00:00</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>这是第2条处理反馈，状态为已处理</t>
-        </is>
-      </c>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3544,21 +6388,34 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -3607,7 +6464,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -3616,12 +6473,25 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -3670,7 +6540,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -3679,12 +6549,25 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -3733,7 +6616,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -3742,12 +6625,25 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -3788,7 +6684,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -3797,24 +6693,25 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>运营人员1</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-06-04 10:00:00</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>这是第4条处理反馈，状态为处理中</t>
-        </is>
-      </c>
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3855,7 +6752,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -3864,12 +6761,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>驳回</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>运营3</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>数据不全无法处理</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3910,7 +6832,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -3919,12 +6841,25 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3965,7 +6900,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -3974,12 +6909,25 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4020,7 +6968,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -4029,12 +6977,25 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4075,7 +7036,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -4084,12 +7045,25 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4130,7 +7104,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -4139,12 +7113,25 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4157,7 +7144,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q18"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4218,30 +7205,45 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
+          <t>超期状态</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>剩余天数</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>建议处理期限</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>处理状态</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>处理人</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>处理时间</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>优先级</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>截止日期</t>
         </is>
@@ -4290,7 +7292,7 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -4299,30 +7301,43 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>已处理</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>运营人员1</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>运营1</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>2025-06-01 10:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>这是第1条处理反馈，状态为已处理</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>已补全缺失日期数据</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4375,7 +7390,7 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -4384,18 +7399,31 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M3" t="n">
+        <v>7</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4448,7 +7476,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -4457,30 +7485,31 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>运营人员3</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>7</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-06-03 10:00:00</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>这是第3条处理反馈，状态为处理中</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4533,7 +7562,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -4542,18 +7571,31 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>7</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4606,7 +7648,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -4615,18 +7657,31 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4675,11 +7730,11 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>复发问题</t>
+          <t>历史未关闭</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -4688,30 +7743,31 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>已处理</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>运营人员2</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M7" t="n">
+        <v>7</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-06-02 10:00:00</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>这是第2条处理反馈，状态为已处理</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4764,27 +7820,40 @@
         </is>
       </c>
       <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
         <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4837,7 +7906,7 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -4846,18 +7915,31 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>7</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4910,7 +7992,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -4919,18 +8001,31 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -4983,7 +8078,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -4992,18 +8087,31 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>7</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5048,7 +8156,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -5057,30 +8165,31 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>处理中</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>运营人员1</t>
-        </is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M12" t="n">
+        <v>7</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-06-04 10:00:00</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>这是第4条处理反馈，状态为处理中</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+          <t>待处理</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5125,7 +8234,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -5134,18 +8243,43 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>待处理</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>7</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>驳回</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>运营3</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:00:00</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>数据不全无法处理</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5190,7 +8324,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -5199,18 +8333,31 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>7</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr">
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5255,7 +8402,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -5264,18 +8411,31 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>7</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5320,7 +8480,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -5329,18 +8489,31 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M16" t="n">
+        <v>7</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5385,7 +8558,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -5394,18 +8567,31 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>7</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5450,7 +8636,7 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -5459,18 +8645,31 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
+          <t>正常</t>
+        </is>
+      </c>
+      <c r="M18" t="n">
+        <v>7</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
           <t>待处理</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
@@ -5545,7 +8744,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>已处理, 待处理</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -5605,7 +8804,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>处理中, 待处理</t>
+          <t>待处理, 驳回</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -5635,7 +8834,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>待处理, 处理中</t>
+          <t>待处理</t>
         </is>
       </c>
       <c r="F5" t="n">
